--- a/5W2H/5W2H-modelo.xlsx
+++ b/5W2H/5W2H-modelo.xlsx
@@ -797,7 +797,7 @@
     <t xml:space="preserve">A escala é igual em todos os dias e não acompanha o pico de pedidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Contratar dois entregadores parceiros para o horário de pico</t>
+    <t xml:space="preserve">Contratar dois entregadores parceiros para o pico; daí em diante, a escala do pico segue os pedidos por faixa de horário medidos na A5</t>
   </si>
   <si>
     <t xml:space="preserve">Tornar obrigatório o complemento do endereço no pedido</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">Gerente de Suprimentos</t>
   </si>
   <si>
-    <t xml:space="preserve">Suprimentos</t>
+    <t xml:space="preserve">Distribuidora de materiais elétricos · Compras</t>
   </si>
   <si>
     <t xml:space="preserve">Equipe de compras</t>
@@ -1954,11 +1954,11 @@
         </c:ser>
         <c:gapWidth val="120"/>
         <c:overlap val="0"/>
-        <c:axId val="79389845"/>
-        <c:axId val="69982321"/>
+        <c:axId val="34601232"/>
+        <c:axId val="20872801"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="79389845"/>
+        <c:axId val="34601232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1990,7 +1990,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69982321"/>
+        <c:crossAx val="20872801"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1998,7 +1998,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69982321"/>
+        <c:axId val="20872801"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2038,7 +2038,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79389845"/>
+        <c:crossAx val="34601232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -4733,12 +4733,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I6:I13" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="O indicador melhora quando sobe ou quando desce?" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G6:G13" type="list">
       <formula1>"Maior é melhor,Menor é melhor"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I6:I13" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Digite apenas o número, sem texto nem unidade." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E6:E13" type="decimal">

--- a/5W2H/5W2H-modelo.xlsx
+++ b/5W2H/5W2H-modelo.xlsx
@@ -1954,11 +1954,11 @@
         </c:ser>
         <c:gapWidth val="120"/>
         <c:overlap val="0"/>
-        <c:axId val="34601232"/>
-        <c:axId val="20872801"/>
+        <c:axId val="52920039"/>
+        <c:axId val="82080472"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34601232"/>
+        <c:axId val="52920039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1990,7 +1990,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20872801"/>
+        <c:crossAx val="82080472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1998,7 +1998,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20872801"/>
+        <c:axId val="82080472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2038,7 +2038,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34601232"/>
+        <c:crossAx val="52920039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
